--- a/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-pothole_tiny_1.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-pothole_tiny_1.xlsx
@@ -7,15 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_s" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_tiny" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_x" sheetId="12" state="visible" r:id="rId12"/>
@@ -596,56 +596,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>62.25267505645752</v>
+        <v>56.4376437664032</v>
       </c>
       <c r="D2" t="n">
-        <v>6.460000038146973</v>
+        <v>15.39000034332275</v>
       </c>
       <c r="E2" t="n">
-        <v>0.145699255772539</v>
+        <v>0.4714817143976688</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5454545617103577</v>
+        <v>0.5714285969734192</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4632352888584137</v>
+        <v>0.3737373650074005</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4292683005332947</v>
+        <v>0.139860138297081</v>
       </c>
       <c r="I2" t="n">
-        <v>0.446601927280426</v>
+        <v>0.1538461595773697</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1010414510965347</v>
+        <v>0.1793380379676818</v>
       </c>
       <c r="K2" t="n">
-        <v>19.88711547851562</v>
+        <v>54.61226010322571</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0368473100662231</v>
+        <v>0.08014402389526359</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0701316118240356</v>
+        <v>0.460851731300354</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07381631851196289</v>
+        <v>0.1720853567123413</v>
       </c>
       <c r="O2" t="n">
-        <v>1.842365503311157</v>
+        <v>4.007201194763184</v>
       </c>
       <c r="P2" t="n">
-        <v>3.506580591201782</v>
+        <v>23.0425865650177</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.690815925598145</v>
+        <v>8.604267835617065</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250627-152714</t>
+          <t>20250725-212216</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -670,22 +670,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -720,53 +720,53 @@
         <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>25.63180613517761</v>
+        <v>67.46666073799133</v>
       </c>
       <c r="D3" t="n">
-        <v>6.480000019073486</v>
+        <v>15.40999984741211</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1435758867140473</v>
+        <v>0.4720881756009726</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4444444477558136</v>
+        <v>0.7142857313156128</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4117647111415863</v>
+        <v>0.4237288236618042</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3880597054958343</v>
+        <v>0.4237288236618042</v>
       </c>
       <c r="I3" t="n">
-        <v>0.410256415605545</v>
+        <v>0.4280442893505096</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0979465842247009</v>
+        <v>0.1791125535964965</v>
       </c>
       <c r="K3" t="n">
-        <v>18.85962843894958</v>
+        <v>54.15538716316223</v>
       </c>
       <c r="L3" t="n">
-        <v>0.041155514717102</v>
+        <v>0.09477213859558099</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0742452907562255</v>
+        <v>0.4563932657241821</v>
       </c>
       <c r="N3" t="n">
-        <v>0.081638445854187</v>
+        <v>0.171515302658081</v>
       </c>
       <c r="O3" t="n">
-        <v>2.057775735855103</v>
+        <v>4.738606929779053</v>
       </c>
       <c r="P3" t="n">
-        <v>3.712264537811279</v>
+        <v>22.8196632862091</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.081922292709351</v>
+        <v>8.575765132904053</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250627-152925</t>
+          <t>20250725-212521</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -791,22 +791,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -838,56 +838,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="C4" t="n">
-        <v>70.09729170799255</v>
+        <v>80.15123176574707</v>
       </c>
       <c r="D4" t="n">
-        <v>6.460000038146973</v>
+        <v>15.40999984741211</v>
       </c>
       <c r="E4" t="n">
-        <v>0.146145399659872</v>
+        <v>0.4731165854369892</v>
       </c>
       <c r="F4" t="n">
-        <v>0.75</v>
+        <v>0.6666666865348816</v>
       </c>
       <c r="G4" t="n">
-        <v>0.410646378993988</v>
+        <v>0.4552845656871795</v>
       </c>
       <c r="H4" t="n">
-        <v>0.404580146074295</v>
+        <v>0.1643835604190826</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4182509481906891</v>
+        <v>0.1756756752729416</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1065522581338882</v>
+        <v>0.1781918853521347</v>
       </c>
       <c r="K4" t="n">
-        <v>18.72127771377563</v>
+        <v>54.80414366722107</v>
       </c>
       <c r="L4" t="n">
-        <v>0.035446982383728</v>
+        <v>0.0804618692398071</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0740448093414306</v>
+        <v>0.4563462018966674</v>
       </c>
       <c r="N4" t="n">
-        <v>0.08027122497558591</v>
+        <v>0.1691587352752685</v>
       </c>
       <c r="O4" t="n">
-        <v>1.772349119186401</v>
+        <v>4.023093461990356</v>
       </c>
       <c r="P4" t="n">
-        <v>3.702240467071533</v>
+        <v>22.81731009483337</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.013561248779297</v>
+        <v>8.457936763763428</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250627-153058</t>
+          <t>20250725-212848</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,56 +959,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>41.43975615501404</v>
+        <v>78.94158864021301</v>
       </c>
       <c r="D5" t="n">
-        <v>6.480000019073486</v>
+        <v>15.40999984741211</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1436606773308344</v>
+        <v>0.472109020632856</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6666666865348816</v>
+        <v>0.5714285969734192</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4308943152427673</v>
+        <v>0.4653061330318451</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3877550959587097</v>
+        <v>0.4242424368858337</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3888888955116272</v>
+        <v>0.4128440320491791</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0933509916067123</v>
+        <v>0.1792281717061996</v>
       </c>
       <c r="K5" t="n">
-        <v>13.55183410644531</v>
+        <v>54.51744937896729</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0399737977981567</v>
+        <v>0.08190140247344969</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07663602828979491</v>
+        <v>0.4617054796218872</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0823387384414672</v>
+        <v>0.1778435850143432</v>
       </c>
       <c r="O5" t="n">
-        <v>1.998689889907837</v>
+        <v>4.095070123672485</v>
       </c>
       <c r="P5" t="n">
-        <v>3.831801414489746</v>
+        <v>23.08527398109436</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.116936922073364</v>
+        <v>8.892179250717163</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250627-153315</t>
+          <t>20250725-213226</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1080,56 +1080,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C6" t="n">
-        <v>38.67496919631958</v>
+        <v>111.7242460250854</v>
       </c>
       <c r="D6" t="n">
-        <v>6.460000038146973</v>
+        <v>15.40999984741211</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1468710858713496</v>
+        <v>0.4720805323853784</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5714285969734192</v>
+        <v>0.6666666865348816</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3523809611797333</v>
+        <v>0.4827586114406585</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3482587039470672</v>
+        <v>0.2435897439718246</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3351351320743561</v>
+        <v>0.1960784345865249</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1106521114706993</v>
+        <v>0.1757216602563858</v>
       </c>
       <c r="K6" t="n">
-        <v>13.34319877624512</v>
+        <v>54.05542540550232</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0389455795288085</v>
+        <v>0.08456116676330561</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0779582786560058</v>
+        <v>0.457063570022583</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08537075042724609</v>
+        <v>0.1716704416275024</v>
       </c>
       <c r="O6" t="n">
-        <v>1.94727897644043</v>
+        <v>4.228058338165283</v>
       </c>
       <c r="P6" t="n">
-        <v>3.897913932800293</v>
+        <v>22.85317850112915</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.268537521362305</v>
+        <v>8.583522081375122</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250627-153459</t>
+          <t>20250725-213554</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1154,22 +1154,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3680,56 +3680,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="C2" t="n">
-        <v>44.65936279296875</v>
+        <v>229.3942382335663</v>
       </c>
       <c r="D2" t="n">
-        <v>9.739999771118164</v>
+        <v>20.65999984741211</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2898756576081117</v>
+        <v>0.5434763961929386</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7692307829856873</v>
+        <v>0.6153846383094788</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4081632792949676</v>
+        <v>0.4824561476707458</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3910614550113678</v>
+        <v>0.4532019793987274</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3867403268814087</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1316933333873748</v>
+        <v>0.1499993205070495</v>
       </c>
       <c r="K2" t="n">
-        <v>54.71559500694275</v>
+        <v>74.73327827453613</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0919853353500366</v>
+        <v>0.0738661241531372</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4562247323989868</v>
+        <v>0.1995673894882202</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1721466159820556</v>
+        <v>0.1870462036132812</v>
       </c>
       <c r="O2" t="n">
-        <v>4.599266767501831</v>
+        <v>3.693306207656861</v>
       </c>
       <c r="P2" t="n">
-        <v>22.81123661994934</v>
+        <v>9.978369474411011</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.607330799102783</v>
+        <v>9.352310180664062</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250629-044937</t>
+          <t>20250724-124435</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -3754,22 +3754,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3801,56 +3801,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="C3" t="n">
-        <v>59.80312156677246</v>
+        <v>303.7026724815369</v>
       </c>
       <c r="D3" t="n">
-        <v>9.760000228881836</v>
+        <v>20.6200008392334</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2883972613250508</v>
+        <v>0.5186671320494119</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6666666865348816</v>
+        <v>0.75</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4534412920475006</v>
+        <v>0.5106382966041565</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3233532905578613</v>
+        <v>0.5094339847564697</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3086419701576233</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1355536133050918</v>
+        <v>0.1485022157430648</v>
       </c>
       <c r="K3" t="n">
-        <v>54.8596556186676</v>
+        <v>80.92131042480469</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0953698205947876</v>
+        <v>0.0673851060867309</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4549046564102172</v>
+        <v>0.2000430488586425</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1715252685546875</v>
+        <v>0.1956958150863647</v>
       </c>
       <c r="O3" t="n">
-        <v>4.76849102973938</v>
+        <v>3.369255304336548</v>
       </c>
       <c r="P3" t="n">
-        <v>22.74523282051086</v>
+        <v>10.00215244293213</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.576263427734375</v>
+        <v>9.784790754318236</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250629-045243</t>
+          <t>20250724-125115</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -3875,22 +3875,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3922,56 +3922,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C4" t="n">
-        <v>61.96865391731262</v>
+        <v>259.7109892368317</v>
       </c>
       <c r="D4" t="n">
-        <v>9.770000457763672</v>
+        <v>21.15999984741211</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2896550096133176</v>
+        <v>0.5160699052470071</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6666666865348816</v>
+        <v>0.5882353186607361</v>
       </c>
       <c r="G4" t="n">
-        <v>0.443708598613739</v>
+        <v>0.4661017060279846</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3274853825569153</v>
+        <v>0.4686192572116852</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3095238208770752</v>
+        <v>0.4418604671955108</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1357670426368713</v>
+        <v>0.1492868959903717</v>
       </c>
       <c r="K4" t="n">
-        <v>54.75327038764954</v>
+        <v>75.17890739440918</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08813389301300049</v>
+        <v>0.0722949934005737</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4554977321624756</v>
+        <v>0.2000106477737426</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1730752325057983</v>
+        <v>0.1885448980331421</v>
       </c>
       <c r="O4" t="n">
-        <v>4.406694650650024</v>
+        <v>3.614749670028687</v>
       </c>
       <c r="P4" t="n">
-        <v>22.77488660812378</v>
+        <v>10.00053238868713</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.653761625289917</v>
+        <v>9.427244901657104</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250629-045605</t>
+          <t>20250724-125909</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4043,56 +4043,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C5" t="n">
-        <v>59.11608362197876</v>
+        <v>291.4932844638824</v>
       </c>
       <c r="D5" t="n">
-        <v>9.760000228881836</v>
+        <v>19.46999931335449</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2897968765567331</v>
+        <v>0.541840021395021</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6153846383094788</v>
+        <v>0.7142857313156128</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4476190507411957</v>
+        <v>0.5154638886451721</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4210526347160339</v>
+        <v>0.5177664756774902</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4120602905750274</v>
+        <v>0.0151515156030654</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1336892545223236</v>
+        <v>0.1479669958353042</v>
       </c>
       <c r="K5" t="n">
-        <v>54.61720705032349</v>
+        <v>81.5724937915802</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0867594099044799</v>
+        <v>0.0787275123596191</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4561832952499389</v>
+        <v>0.2110380601882934</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1715158224105835</v>
+        <v>0.2102548599243164</v>
       </c>
       <c r="O5" t="n">
-        <v>4.337970495223999</v>
+        <v>3.936375617980957</v>
       </c>
       <c r="P5" t="n">
-        <v>22.80916476249695</v>
+        <v>10.55190300941467</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.575791120529175</v>
+        <v>10.51274299621582</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250629-045928</t>
+          <t>20250724-130619</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4117,22 +4117,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4164,56 +4164,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C6" t="n">
-        <v>42.53421783447266</v>
+        <v>250.0705108642578</v>
       </c>
       <c r="D6" t="n">
-        <v>9.720000267028809</v>
+        <v>20.98999977111816</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2892502335210641</v>
+        <v>0.5345196563463944</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6153846383094788</v>
+        <v>0.8571428656578064</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3356643319129944</v>
+        <v>0.5042017102241516</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2560975551605224</v>
+        <v>0.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.25</v>
+        <v>0.5074626803398132</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1300512552261352</v>
+        <v>0.1504928022623062</v>
       </c>
       <c r="K6" t="n">
-        <v>54.50159668922424</v>
+        <v>81.13489270210266</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08822496891021719</v>
+        <v>0.069381308555603</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4552542066574097</v>
+        <v>0.1986098718643188</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1717015790939331</v>
+        <v>0.1896312427520751</v>
       </c>
       <c r="O6" t="n">
-        <v>4.411248445510864</v>
+        <v>3.469065427780152</v>
       </c>
       <c r="P6" t="n">
-        <v>22.76271033287048</v>
+        <v>9.930493593215942</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.585078954696655</v>
+        <v>9.48156213760376</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250629-050247</t>
+          <t>20250724-131352</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -4238,22 +4238,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4451,56 +4451,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C2" t="n">
-        <v>246.691900730133</v>
+        <v>248.7876675128937</v>
       </c>
       <c r="D2" t="n">
-        <v>14.27000045776367</v>
+        <v>10.02000045776367</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4834353644114274</v>
+        <v>0.3143638484790677</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6666666865348816</v>
+        <v>0.5714285969734192</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4864864945411682</v>
+        <v>0.3482587039470672</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4285714328289032</v>
+        <v>0.3409090936183929</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.3687150776386261</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1331716328859329</v>
+        <v>0.1762672364711761</v>
       </c>
       <c r="K2" t="n">
-        <v>82.00321531295776</v>
+        <v>51.33298349380493</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0816130208969116</v>
+        <v>0.076555585861206</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1975923871994018</v>
+        <v>0.2199510049819946</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1889404344558715</v>
+        <v>0.1814845609664917</v>
       </c>
       <c r="O2" t="n">
-        <v>4.080651044845581</v>
+        <v>3.827779293060303</v>
       </c>
       <c r="P2" t="n">
-        <v>9.879619359970093</v>
+        <v>10.99755024909973</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.447021722793581</v>
+        <v>9.074228048324583</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250628-095608</t>
+          <t>20250726-224520</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -4525,22 +4525,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4572,56 +4572,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="C3" t="n">
-        <v>237.1697330474853</v>
+        <v>199.2726721763611</v>
       </c>
       <c r="D3" t="n">
-        <v>14.63000011444092</v>
+        <v>9.960000038146973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4625864780866183</v>
+        <v>0.3040947531368218</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6666666865348816</v>
+        <v>0.4285714328289032</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5317460298538208</v>
+        <v>0.2416666597127914</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5248869061470032</v>
+        <v>0.2124542146921157</v>
       </c>
       <c r="I3" t="n">
-        <v>0.549763023853302</v>
+        <v>0.2222222238779068</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1374081373214721</v>
+        <v>0.1750929951667785</v>
       </c>
       <c r="K3" t="n">
-        <v>81.24207949638367</v>
+        <v>44.99414110183716</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0878865385055542</v>
+        <v>0.0735672330856323</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2052267122268676</v>
+        <v>0.2199038743972778</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2020034551620483</v>
+        <v>0.1728530931472778</v>
       </c>
       <c r="O3" t="n">
-        <v>4.39432692527771</v>
+        <v>3.678361654281616</v>
       </c>
       <c r="P3" t="n">
-        <v>10.26133561134338</v>
+        <v>10.99519371986389</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.10017275810242</v>
+        <v>8.642654657363892</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250628-100306</t>
+          <t>20250726-225146</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -4646,22 +4646,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4693,56 +4693,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C4" t="n">
-        <v>270.7737419605255</v>
+        <v>247.1399891376496</v>
       </c>
       <c r="D4" t="n">
-        <v>14.22000026702881</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4599223984139306</v>
+        <v>0.3039928369346212</v>
       </c>
       <c r="F4" t="n">
-        <v>0.800000011920929</v>
+        <v>0.4000000059604645</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5381526350975037</v>
+        <v>0.4401544332504272</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5317460298538208</v>
+        <v>0.1538461595773697</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5428571701049805</v>
+        <v>0.0875912383198738</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1322997957468032</v>
+        <v>0.1781171560287475</v>
       </c>
       <c r="K4" t="n">
-        <v>81.16891169548035</v>
+        <v>51.04117751121521</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0848448991775512</v>
+        <v>0.0833243989944458</v>
       </c>
       <c r="M4" t="n">
-        <v>0.203537049293518</v>
+        <v>0.2193664979934692</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1897446823120117</v>
+        <v>0.1802127933502197</v>
       </c>
       <c r="O4" t="n">
-        <v>4.242244958877564</v>
+        <v>4.16621994972229</v>
       </c>
       <c r="P4" t="n">
-        <v>10.1768524646759</v>
+        <v>10.96832489967346</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.487234115600586</v>
+        <v>9.010639667510986</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250628-100944</t>
+          <t>20250726-225721</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -4767,22 +4767,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4814,56 +4814,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="C5" t="n">
-        <v>236.8696722984314</v>
+        <v>175.6378319263459</v>
       </c>
       <c r="D5" t="n">
-        <v>14.25</v>
+        <v>9.710000038146973</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4791176524013281</v>
+        <v>0.3166931375514629</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>0.4285714328289032</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4961832165718078</v>
+        <v>0.1931818127632141</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4069767296314239</v>
+        <v>0.1587301641702652</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.0784313753247261</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1408320963382721</v>
+        <v>0.1721145957708358</v>
       </c>
       <c r="K5" t="n">
-        <v>75.34917831420898</v>
+        <v>51.12091016769409</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08730240345001219</v>
+        <v>0.0728825330734252</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2001060342788696</v>
+        <v>0.218329701423645</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1961603832244873</v>
+        <v>0.1854470539093017</v>
       </c>
       <c r="O5" t="n">
-        <v>4.36512017250061</v>
+        <v>3.644126653671265</v>
       </c>
       <c r="P5" t="n">
-        <v>10.00530171394348</v>
+        <v>10.91648507118225</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.808019161224363</v>
+        <v>9.272352695465088</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250628-101706</t>
+          <t>20250726-230344</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4888,22 +4888,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4935,56 +4935,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="C6" t="n">
-        <v>245.7350397109985</v>
+        <v>166.4595348834992</v>
       </c>
       <c r="D6" t="n">
-        <v>14.53999996185303</v>
+        <v>10.10999965667725</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4741827926852486</v>
+        <v>0.3094118570172509</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6666666865348816</v>
+        <v>0.5454545617103577</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4594594538211822</v>
+        <v>0.233333334326744</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4576271176338196</v>
+        <v>0.1829268336296081</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.0839160829782486</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1318594366312027</v>
+        <v>0.1678855121135711</v>
       </c>
       <c r="K6" t="n">
-        <v>80.97663855552673</v>
+        <v>50.93625855445862</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0844631195068359</v>
+        <v>0.07654171466827391</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2060906076431274</v>
+        <v>0.2163513898849487</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2000309705734252</v>
+        <v>0.1841522455215454</v>
       </c>
       <c r="O6" t="n">
-        <v>4.223155975341797</v>
+        <v>3.827085733413696</v>
       </c>
       <c r="P6" t="n">
-        <v>10.30453038215637</v>
+        <v>10.81756949424744</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.00154852867126</v>
+        <v>9.207612276077271</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250628-102349</t>
+          <t>20250726-230846</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5009,22 +5009,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5222,56 +5222,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>215.0854599475861</v>
+        <v>80.57877588272095</v>
       </c>
       <c r="D2" t="n">
-        <v>9.460000038146973</v>
+        <v>5.519999980926514</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2952613041681401</v>
+        <v>0.1517278710007667</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>0.4285714328289032</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3919597864151001</v>
+        <v>0.1722113490104675</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3728813529014587</v>
+        <v>0.1949685513973236</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2179487198591232</v>
+        <v>0.1108312308788299</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1469234973192215</v>
+        <v>0.0922111198306083</v>
       </c>
       <c r="K2" t="n">
-        <v>51.49350237846375</v>
+        <v>24.34444427490234</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0989718770980835</v>
+        <v>0.0487195062637329</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2182849168777466</v>
+        <v>0.0782271242141723</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1819821691513061</v>
+        <v>0.0867596721649169</v>
       </c>
       <c r="O2" t="n">
-        <v>4.948593854904175</v>
+        <v>2.435975313186645</v>
       </c>
       <c r="P2" t="n">
-        <v>10.91424584388733</v>
+        <v>3.911356210708618</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.099108457565308</v>
+        <v>4.33798360824585</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-001853</t>
+          <t>20250728-034835</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -5296,22 +5296,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5343,56 +5343,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C3" t="n">
-        <v>223.6700565814972</v>
+        <v>74.75043487548828</v>
       </c>
       <c r="D3" t="n">
-        <v>8.960000038146973</v>
+        <v>5.21999979019165</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2870981510857056</v>
+        <v>0.151398325131999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4000000059604645</v>
+        <v>0.5454545617103577</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2056074738502502</v>
+        <v>0.2131147533655166</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2456140369176864</v>
+        <v>0.1492537260055542</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1382978707551956</v>
+        <v>0.0823529437184333</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1456069052219391</v>
+        <v>0.09264492243528361</v>
       </c>
       <c r="K3" t="n">
-        <v>52.0149073600769</v>
+        <v>24.22022652626038</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0843929815292358</v>
+        <v>0.0470314693450927</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2243774032592773</v>
+        <v>0.0783754444122314</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1735248279571533</v>
+        <v>0.0861108684539794</v>
       </c>
       <c r="O3" t="n">
-        <v>4.219649076461792</v>
+        <v>2.351573467254639</v>
       </c>
       <c r="P3" t="n">
-        <v>11.21887016296387</v>
+        <v>3.918772220611572</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.676241397857666</v>
+        <v>4.305543422698975</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-002448</t>
+          <t>20250728-035114</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -5417,22 +5417,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5464,56 +5464,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C4" t="n">
-        <v>168.3935794830322</v>
+        <v>83.11661720275879</v>
       </c>
       <c r="D4" t="n">
-        <v>9.220000267028809</v>
+        <v>5.550000190734863</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2862145801385243</v>
+        <v>0.1488993843948399</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6153846383094788</v>
+        <v>0.4000000059604645</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4561403393745422</v>
+        <v>0.1297709941864013</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3728813529014587</v>
+        <v>0.145454540848732</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3555555641651153</v>
+        <v>0.1199999973177909</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1516481935977935</v>
+        <v>0.0898006334900856</v>
       </c>
       <c r="K4" t="n">
-        <v>51.25061225891113</v>
+        <v>24.66922974586487</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0889333343505859</v>
+        <v>0.0468708705902099</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2190805101394653</v>
+        <v>0.07913556098937979</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1858310031890869</v>
+        <v>0.0829643821716308</v>
       </c>
       <c r="O4" t="n">
-        <v>4.446666717529297</v>
+        <v>2.343543529510498</v>
       </c>
       <c r="P4" t="n">
-        <v>10.95402550697327</v>
+        <v>3.956778049468994</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.291550159454346</v>
+        <v>4.148219108581543</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-003049</t>
+          <t>20250728-035348</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -5538,22 +5538,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5585,56 +5585,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C5" t="n">
-        <v>174.5580551624298</v>
+        <v>106.3990228176117</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>5.360000133514404</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2937829935170234</v>
+        <v>0.1505358728809633</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4000000059604645</v>
+        <v>0.5454545617103577</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3041824996471405</v>
+        <v>0.3813559412956238</v>
       </c>
       <c r="H5" t="n">
-        <v>0.24870465695858</v>
+        <v>0.3497267663478851</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2643678188323974</v>
+        <v>0.2828282713890075</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1466541886329651</v>
+        <v>0.09456852823495859</v>
       </c>
       <c r="K5" t="n">
-        <v>51.3846116065979</v>
+        <v>24.40495848655701</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08801135540008539</v>
+        <v>0.0526890230178833</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2181313800811767</v>
+        <v>0.0853465700149536</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1872869253158569</v>
+        <v>0.08557775497436521</v>
       </c>
       <c r="O5" t="n">
-        <v>4.400567770004272</v>
+        <v>2.634451150894165</v>
       </c>
       <c r="P5" t="n">
-        <v>10.90656900405884</v>
+        <v>4.267328500747681</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.364346265792848</v>
+        <v>4.278887748718262</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-003545</t>
+          <t>20250728-035629</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -5659,22 +5659,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5706,56 +5706,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>219.2621121406555</v>
+        <v>77.44403624534607</v>
       </c>
       <c r="D6" t="n">
-        <v>9.199999809265137</v>
+        <v>5.599999904632568</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2864394088586171</v>
+        <v>0.153107589110732</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.4000000059604645</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3398058116436004</v>
+        <v>0.2510822415351867</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3113772571086883</v>
+        <v>0.0444444455206394</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2013422846794128</v>
+        <v>0.0724637657403945</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1524917185306549</v>
+        <v>0.0762060657143592</v>
       </c>
       <c r="K6" t="n">
-        <v>51.27015376091003</v>
+        <v>24.30633473396301</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08434816837310791</v>
+        <v>0.0454163742065429</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2260755777359008</v>
+        <v>0.0793593549728393</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1731179332733154</v>
+        <v>0.0971490430831909</v>
       </c>
       <c r="O6" t="n">
-        <v>4.217408418655396</v>
+        <v>2.270818710327148</v>
       </c>
       <c r="P6" t="n">
-        <v>11.30377888679504</v>
+        <v>3.967967748641968</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.655896663665771</v>
+        <v>4.857452154159546</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-004048</t>
+          <t>20250728-035934</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5780,22 +5780,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5993,56 +5993,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C2" t="n">
-        <v>82.43288898468018</v>
+        <v>160.2129647731781</v>
       </c>
       <c r="D2" t="n">
-        <v>3.220000028610229</v>
+        <v>8.119999885559082</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1631872061226102</v>
+        <v>0.2456420833865801</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5454545617103577</v>
+        <v>0.6666666865348816</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2247191071510315</v>
+        <v>0.3618090450763702</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2368421107530594</v>
+        <v>0.3692307770252228</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1946902722120285</v>
+        <v>0.314814805984497</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0831781178712844</v>
+        <v>0.1354532390832901</v>
       </c>
       <c r="K2" t="n">
-        <v>24.52091717720032</v>
+        <v>38.8638801574707</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0499673128128051</v>
+        <v>0.0586934328079223</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07929934501647939</v>
+        <v>0.1444100666046142</v>
       </c>
       <c r="N2" t="n">
-        <v>0.09088436126708981</v>
+        <v>0.150786862373352</v>
       </c>
       <c r="O2" t="n">
-        <v>2.498365640640259</v>
+        <v>2.934671640396118</v>
       </c>
       <c r="P2" t="n">
-        <v>3.964967250823975</v>
+        <v>7.220503330230713</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.544218063354492</v>
+        <v>7.539343118667602</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-160718</t>
+          <t>20250729-065151</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6067,22 +6067,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6114,56 +6114,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" t="n">
-        <v>80.34795498847961</v>
+        <v>110.3478984832764</v>
       </c>
       <c r="D3" t="n">
-        <v>3.059999942779541</v>
+        <v>6.650000095367432</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1651160852160564</v>
+        <v>0.2407632429491389</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6153846383094788</v>
+        <v>0.4000000059604645</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3529411852359772</v>
+        <v>0.3362831771373749</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3517588078975677</v>
+        <v>0.2292993664741516</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2977099120616913</v>
+        <v>0.1621621549129486</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0877156630158424</v>
+        <v>0.1324339658021927</v>
       </c>
       <c r="K3" t="n">
-        <v>24.50898432731628</v>
+        <v>38.65304660797119</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0501698160171508</v>
+        <v>0.0573437595367431</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0794307231903076</v>
+        <v>0.143456220626831</v>
       </c>
       <c r="N3" t="n">
-        <v>0.08354288578033441</v>
+        <v>0.1466801023483276</v>
       </c>
       <c r="O3" t="n">
-        <v>2.508490800857544</v>
+        <v>2.867187976837158</v>
       </c>
       <c r="P3" t="n">
-        <v>3.971536159515381</v>
+        <v>7.172811031341553</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.177144289016724</v>
+        <v>7.334005117416382</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-161000</t>
+          <t>20250729-065620</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6188,22 +6188,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -6235,56 +6235,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C4" t="n">
-        <v>79.37204360961914</v>
+        <v>105.8199727535248</v>
       </c>
       <c r="D4" t="n">
-        <v>3.210000038146973</v>
+        <v>7.75</v>
       </c>
       <c r="E4" t="n">
-        <v>0.161477197771487</v>
+        <v>0.2389212444771168</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5454545617103577</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1941747516393661</v>
+        <v>0.2758620679378509</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1922077983617782</v>
+        <v>0.259740263223648</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1923076957464218</v>
+        <v>0.2645914256572723</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0869633927941322</v>
+        <v>0.1314540356397628</v>
       </c>
       <c r="K4" t="n">
-        <v>24.75374937057495</v>
+        <v>39.75990915298462</v>
       </c>
       <c r="L4" t="n">
-        <v>0.052102313041687</v>
+        <v>0.0658135366439819</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0794097375869751</v>
+        <v>0.1376559352874755</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0884741830825805</v>
+        <v>0.1389776945114135</v>
       </c>
       <c r="O4" t="n">
-        <v>2.605115652084351</v>
+        <v>3.290676832199097</v>
       </c>
       <c r="P4" t="n">
-        <v>3.970486879348755</v>
+        <v>6.882796764373779</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.423709154129028</v>
+        <v>6.948884725570679</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-161240</t>
+          <t>20250729-065958</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -6356,56 +6356,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="n">
-        <v>74.9568829536438</v>
+        <v>112.3639140129089</v>
       </c>
       <c r="D5" t="n">
-        <v>3.029999971389771</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1651854756805631</v>
+        <v>0.2461951178583231</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4000000059604645</v>
+        <v>0.5333333611488342</v>
       </c>
       <c r="G5" t="n">
-        <v>0.149732619524002</v>
+        <v>0.2910798192024231</v>
       </c>
       <c r="H5" t="n">
-        <v>0.132492110133171</v>
+        <v>0.2727272808551788</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1125541105866432</v>
+        <v>0.2980392277240753</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0902046039700508</v>
+        <v>0.1242554932832717</v>
       </c>
       <c r="K5" t="n">
-        <v>24.19412541389465</v>
+        <v>39.38969278335571</v>
       </c>
       <c r="L5" t="n">
-        <v>0.057482099533081</v>
+        <v>0.0600435400009155</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0794300985336303</v>
+        <v>0.1398304033279419</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1006067132949829</v>
+        <v>0.1432393169403076</v>
       </c>
       <c r="O5" t="n">
-        <v>2.874104976654053</v>
+        <v>3.002177000045776</v>
       </c>
       <c r="P5" t="n">
-        <v>3.971504926681519</v>
+        <v>6.991520166397095</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.030335664749146</v>
+        <v>7.161965847015381</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-161519</t>
+          <t>20250729-070333</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -6430,22 +6430,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -6477,56 +6477,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C6" t="n">
-        <v>74.24191117286682</v>
+        <v>146.5834906101227</v>
       </c>
       <c r="D6" t="n">
-        <v>3.140000104904175</v>
+        <v>7.340000152587891</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1645289701084757</v>
+        <v>0.2423467474250958</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4285714328289032</v>
+        <v>0.5454545617103577</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1525423675775528</v>
+        <v>0.3539822995662689</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1573770493268966</v>
+        <v>0.3317073285579681</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1264367848634719</v>
+        <v>0.3441860377788543</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0915776565670967</v>
+        <v>0.1327916085720062</v>
       </c>
       <c r="K6" t="n">
-        <v>24.48744440078736</v>
+        <v>40.04900884628296</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0523200845718383</v>
+        <v>0.057421326637268</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07942027091979981</v>
+        <v>0.1382540607452392</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0950314378738403</v>
+        <v>0.1397407436370849</v>
       </c>
       <c r="O6" t="n">
-        <v>2.616004228591919</v>
+        <v>2.871066331863404</v>
       </c>
       <c r="P6" t="n">
-        <v>3.97101354598999</v>
+        <v>6.912703037261963</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.751571893692017</v>
+        <v>6.987037181854248</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-161744</t>
+          <t>20250729-070714</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -6551,22 +6551,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -6764,56 +6764,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="C2" t="n">
-        <v>123.9803192615509</v>
+        <v>83.63645386695862</v>
       </c>
       <c r="D2" t="n">
-        <v>7.039999961853027</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2508476431603017</v>
+        <v>0.1366420787974045</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>0.5333333611488342</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2639999985694885</v>
+        <v>0.3574144542217254</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2169811278581619</v>
+        <v>0.3546797931194305</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2571428716182709</v>
+        <v>0.3513513505458832</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1250864267349243</v>
+        <v>0.0894577130675315</v>
       </c>
       <c r="K2" t="n">
-        <v>39.18950605392456</v>
+        <v>13.86655712127686</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0741528272628784</v>
+        <v>0.0383311653137207</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1391646909713745</v>
+        <v>0.0466747236251831</v>
       </c>
       <c r="N2" t="n">
-        <v>0.141001009941101</v>
+        <v>0.0402847385406494</v>
       </c>
       <c r="O2" t="n">
-        <v>3.707641363143921</v>
+        <v>1.916558265686035</v>
       </c>
       <c r="P2" t="n">
-        <v>6.958234548568726</v>
+        <v>2.333736181259156</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.050050497055054</v>
+        <v>2.014236927032471</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-034619</t>
+          <t>20250730-080922</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6838,22 +6838,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6885,56 +6885,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="C3" t="n">
-        <v>146.4493250846863</v>
+        <v>88.36796879768372</v>
       </c>
       <c r="D3" t="n">
-        <v>5.960000038146973</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2440675826005215</v>
+        <v>0.1365963245203735</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.6153846383094788</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3068782985210418</v>
+        <v>0.3277311027050018</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3137255012989044</v>
+        <v>0.3174603283405304</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2162162214517593</v>
+        <v>0.304347813129425</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1124795079231262</v>
+        <v>0.1136086955666542</v>
       </c>
       <c r="K3" t="n">
-        <v>33.22668266296387</v>
+        <v>14.01389718055725</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0636613273620605</v>
+        <v>0.0392447233200073</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1410659742355346</v>
+        <v>0.0477810716629028</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1475924682617187</v>
+        <v>0.0410291528701782</v>
       </c>
       <c r="O3" t="n">
-        <v>3.183066368103028</v>
+        <v>1.962236166000366</v>
       </c>
       <c r="P3" t="n">
-        <v>7.053298711776733</v>
+        <v>2.389053583145142</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.379623413085938</v>
+        <v>2.051457643508911</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-035013</t>
+          <t>20250730-081140</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6959,22 +6959,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7006,56 +7006,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C4" t="n">
-        <v>123.9910800457001</v>
+        <v>45.35214376449585</v>
       </c>
       <c r="D4" t="n">
-        <v>6.699999809265137</v>
+        <v>10.43000030517578</v>
       </c>
       <c r="E4" t="n">
-        <v>0.244986680538758</v>
+        <v>0.1358605692232096</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4444444477558136</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3063063025474548</v>
+        <v>0.2062499970197677</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2792452871799469</v>
+        <v>0.1428571492433548</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2489959895610809</v>
+        <v>0.1452513933181762</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1184343919157981</v>
+        <v>0.0913845896720886</v>
       </c>
       <c r="K4" t="n">
-        <v>39.58295297622681</v>
+        <v>13.81914472579956</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0650275897979736</v>
+        <v>0.0451998996734619</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1392283773422241</v>
+        <v>0.0472572755813598</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1405863857269287</v>
+        <v>0.040804443359375</v>
       </c>
       <c r="O4" t="n">
-        <v>3.251379489898682</v>
+        <v>2.259994983673096</v>
       </c>
       <c r="P4" t="n">
-        <v>6.961418867111206</v>
+        <v>2.362863779067993</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.029319286346436</v>
+        <v>2.04022216796875</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-035430</t>
+          <t>20250730-081402</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7080,22 +7080,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7127,56 +7127,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="C5" t="n">
-        <v>120.8178334236145</v>
+        <v>87.01511192321777</v>
       </c>
       <c r="D5" t="n">
-        <v>6.019999980926514</v>
+        <v>10.43000030517578</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2458764969609504</v>
+        <v>0.1362298405771955</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6666666865348816</v>
+        <v>0.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4369747936725616</v>
+        <v>0.2575107216835022</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4424778819084167</v>
+        <v>0.2038216590881347</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4465116262435913</v>
+        <v>0.1733333319425583</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1163775324821472</v>
+        <v>0.09808877110481259</v>
       </c>
       <c r="K5" t="n">
-        <v>38.8225257396698</v>
+        <v>13.83750629425049</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07188004970550529</v>
+        <v>0.037680230140686</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1393239974975585</v>
+        <v>0.0473639249801635</v>
       </c>
       <c r="N5" t="n">
-        <v>0.142754168510437</v>
+        <v>0.0402066135406494</v>
       </c>
       <c r="O5" t="n">
-        <v>3.594002485275269</v>
+        <v>1.884011507034302</v>
       </c>
       <c r="P5" t="n">
-        <v>6.96619987487793</v>
+        <v>2.368196249008179</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.137708425521851</v>
+        <v>2.010330677032471</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-035824</t>
+          <t>20250730-081542</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7201,22 +7201,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -7248,56 +7248,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C6" t="n">
-        <v>123.4236671924591</v>
+        <v>60.33100199699402</v>
       </c>
       <c r="D6" t="n">
-        <v>6.440000057220459</v>
+        <v>10.43000030517578</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2453205202790823</v>
+        <v>0.1362124635158358</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6153846383094788</v>
+        <v>0.5454545617103577</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4481327831745147</v>
+        <v>0.2970297038555145</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4769230782985687</v>
+        <v>0.1506849378347396</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3540669977664947</v>
+        <v>0.1506849378347396</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1178541481494903</v>
+        <v>0.1078329384326934</v>
       </c>
       <c r="K6" t="n">
-        <v>39.80645203590393</v>
+        <v>13.59879493713379</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0641792011260986</v>
+        <v>0.0369692182540893</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1388362026214599</v>
+        <v>0.0475083112716674</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1449743127822876</v>
+        <v>0.0397218465805053</v>
       </c>
       <c r="O6" t="n">
-        <v>3.208960056304932</v>
+        <v>1.848460912704468</v>
       </c>
       <c r="P6" t="n">
-        <v>6.941810131072998</v>
+        <v>2.375415563583374</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.24871563911438</v>
+        <v>1.986092329025269</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-040214</t>
+          <t>20250730-081803</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -7322,22 +7322,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -7535,56 +7535,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="C2" t="n">
-        <v>47.35507535934448</v>
+        <v>140.6317574977875</v>
       </c>
       <c r="D2" t="n">
-        <v>1.679999947547913</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1093312573887533</v>
+        <v>0.2387125374328705</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5714285969734192</v>
+        <v>0.7692307829856873</v>
       </c>
       <c r="G2" t="n">
-        <v>0.402010053396225</v>
+        <v>0.3666666746139526</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3894736766815185</v>
+        <v>0.3664921522140503</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2569832503795624</v>
+        <v>0.3350785374641418</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09124407917261119</v>
+        <v>0.1104689911007881</v>
       </c>
       <c r="K2" t="n">
-        <v>9.597659587860107</v>
+        <v>29.85559487342834</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0438233089447021</v>
+        <v>0.0441652345657348</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0522859764099121</v>
+        <v>0.1290111017227173</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0555906820297241</v>
+        <v>0.1002746868133545</v>
       </c>
       <c r="O2" t="n">
-        <v>2.191165447235107</v>
+        <v>2.208261728286743</v>
       </c>
       <c r="P2" t="n">
-        <v>2.614298820495605</v>
+        <v>6.450555086135864</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.779534101486206</v>
+        <v>5.013734340667725</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-175719</t>
+          <t>20250731-004714</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -7609,22 +7609,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -7656,56 +7656,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C3" t="n">
-        <v>58.06486487388611</v>
+        <v>90.02038931846619</v>
       </c>
       <c r="D3" t="n">
-        <v>1.700000047683716</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="E3" t="n">
-        <v>0.108183067694709</v>
+        <v>0.2380941248015512</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5454545617103577</v>
+        <v>0.5882353186607361</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3636363744735718</v>
+        <v>0.4387755095958709</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2696629166603088</v>
+        <v>0.4622641503810882</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2476190477609634</v>
+        <v>0.4881889820098877</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0845824927091598</v>
+        <v>0.09813341498374931</v>
       </c>
       <c r="K3" t="n">
-        <v>15.36320495605469</v>
+        <v>29.65883421897888</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0424841737747192</v>
+        <v>0.0425856637954711</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0449059391021728</v>
+        <v>0.1309100484848022</v>
       </c>
       <c r="N3" t="n">
-        <v>0.057069764137268</v>
+        <v>0.0911392068862915</v>
       </c>
       <c r="O3" t="n">
-        <v>2.124208688735962</v>
+        <v>2.12928318977356</v>
       </c>
       <c r="P3" t="n">
-        <v>2.245296955108643</v>
+        <v>6.545502424240112</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.853488206863404</v>
+        <v>4.556960344314575</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-175859</t>
+          <t>20250731-005052</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7777,56 +7777,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="C4" t="n">
-        <v>69.97928071022034</v>
+        <v>51.75256037712097</v>
       </c>
       <c r="D4" t="n">
-        <v>1.730000019073486</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1094247883792673</v>
+        <v>0.2376892722465775</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>0.4615384638309479</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3507462739944458</v>
+        <v>0.3181818127632141</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2119205296039581</v>
+        <v>0.25</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2564102709293365</v>
+        <v>0.2473118305206298</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07790890336036679</v>
+        <v>0.0938628762960434</v>
       </c>
       <c r="K4" t="n">
-        <v>15.18374991416931</v>
+        <v>24.05821013450623</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0431840229034423</v>
+        <v>0.0504403114318847</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0457931900024414</v>
+        <v>0.1290861797332763</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0575720357894897</v>
+        <v>0.0896656656265258</v>
       </c>
       <c r="O4" t="n">
-        <v>2.159201145172119</v>
+        <v>2.522015571594238</v>
       </c>
       <c r="P4" t="n">
-        <v>2.28965950012207</v>
+        <v>6.454308986663818</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.878601789474488</v>
+        <v>4.483283281326294</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-180056</t>
+          <t>20250731-005348</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7851,22 +7851,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7898,56 +7898,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="C5" t="n">
-        <v>43.8674783706665</v>
+        <v>84.54476761817932</v>
       </c>
       <c r="D5" t="n">
-        <v>1.679999947547913</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1095885615105981</v>
+        <v>0.2378032720974973</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6153846383094788</v>
+        <v>0.5714285969734192</v>
       </c>
       <c r="G5" t="n">
-        <v>0.409090906381607</v>
+        <v>0.3833865821361542</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3655914068222046</v>
+        <v>0.3478260934352875</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3617021143436432</v>
+        <v>0.3488371968269348</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0862606987357139</v>
+        <v>0.0995197519659996</v>
       </c>
       <c r="K5" t="n">
-        <v>9.615137100219728</v>
+        <v>29.62205600738525</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0498618030548095</v>
+        <v>0.0432234525680541</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0448733615875244</v>
+        <v>0.1256285810470581</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0631472969055175</v>
+        <v>0.09908814907073971</v>
       </c>
       <c r="O5" t="n">
-        <v>2.493090152740479</v>
+        <v>2.16117262840271</v>
       </c>
       <c r="P5" t="n">
-        <v>2.243668079376221</v>
+        <v>6.281429052352905</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.157364845275879</v>
+        <v>4.954407453536987</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-180304</t>
+          <t>20250731-005605</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7972,22 +7972,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -8019,56 +8019,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C6" t="n">
-        <v>31.81498122215271</v>
+        <v>63.21122097969055</v>
       </c>
       <c r="D6" t="n">
-        <v>1.679999947547913</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1065796220149749</v>
+        <v>0.2377764199067045</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3636363744735718</v>
+        <v>0.6666666865348816</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2842105329036712</v>
+        <v>0.276422768831253</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2622950673103332</v>
+        <v>0.211764708161354</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2555555701255798</v>
+        <v>0.2022471874952316</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1333552151918411</v>
+        <v>0.0988862216472625</v>
       </c>
       <c r="K6" t="n">
-        <v>9.734108448028564</v>
+        <v>29.61970210075378</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0471098804473876</v>
+        <v>0.0392264652252197</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0447437477111816</v>
+        <v>0.1299945402145385</v>
       </c>
       <c r="N6" t="n">
-        <v>0.06300902366638179</v>
+        <v>0.0899279022216796</v>
       </c>
       <c r="O6" t="n">
-        <v>2.355494022369385</v>
+        <v>1.961323261260986</v>
       </c>
       <c r="P6" t="n">
-        <v>2.237187385559082</v>
+        <v>6.499727010726929</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.150451183319092</v>
+        <v>4.496395111083984</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-180446</t>
+          <t>20250731-005846</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8306,56 +8306,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="C2" t="n">
-        <v>44.2421350479126</v>
+        <v>62.25267505645752</v>
       </c>
       <c r="D2" t="n">
-        <v>5.349999904632568</v>
+        <v>6.460000038146973</v>
       </c>
       <c r="E2" t="n">
-        <v>0.100992123423903</v>
+        <v>0.145699255772539</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>0.5454545617103577</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2436548173427581</v>
+        <v>0.4632352888584137</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2458100616931915</v>
+        <v>0.4292683005332947</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2539682686328888</v>
+        <v>0.446601927280426</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09489629417657849</v>
+        <v>0.1010414510965347</v>
       </c>
       <c r="K2" t="n">
-        <v>13.83706474304199</v>
+        <v>19.88711547851562</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0495518779754638</v>
+        <v>0.0368473100662231</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0476374864578247</v>
+        <v>0.0701316118240356</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0412178325653076</v>
+        <v>0.07381631851196289</v>
       </c>
       <c r="O2" t="n">
-        <v>2.477593898773193</v>
+        <v>1.842365503311157</v>
       </c>
       <c r="P2" t="n">
-        <v>2.381874322891236</v>
+        <v>3.506580591201782</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.060891628265381</v>
+        <v>3.690815925598145</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250702-073505</t>
+          <t>20250627-152714</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -8427,56 +8427,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>124</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>94.09567284584044</v>
+        <v>25.63180613517761</v>
       </c>
       <c r="D3" t="n">
-        <v>5.349999904632568</v>
+        <v>6.480000019073486</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1022786469829659</v>
+        <v>0.1435758867140473</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6153846383094788</v>
+        <v>0.4444444477558136</v>
       </c>
       <c r="G3" t="n">
-        <v>0.347169816493988</v>
+        <v>0.4117647111415863</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2666666805744171</v>
+        <v>0.3880597054958343</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2666666805744171</v>
+        <v>0.410256415605545</v>
       </c>
       <c r="J3" t="n">
-        <v>0.093192771077156</v>
+        <v>0.0979465842247009</v>
       </c>
       <c r="K3" t="n">
-        <v>8.27849006652832</v>
+        <v>18.85962843894958</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0395371341705322</v>
+        <v>0.041155514717102</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0557077836990356</v>
+        <v>0.0742452907562255</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0413260841369628</v>
+        <v>0.081638445854187</v>
       </c>
       <c r="O3" t="n">
-        <v>1.976856708526612</v>
+        <v>2.057775735855103</v>
       </c>
       <c r="P3" t="n">
-        <v>2.785389184951782</v>
+        <v>3.712264537811279</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.066304206848145</v>
+        <v>4.081922292709351</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250702-073644</t>
+          <t>20250627-152925</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -8548,56 +8548,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="C4" t="n">
-        <v>49.53020429611206</v>
+        <v>70.09729170799255</v>
       </c>
       <c r="D4" t="n">
-        <v>5.349999904632568</v>
+        <v>6.460000038146973</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1000853333389386</v>
+        <v>0.146145399659872</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2727272808551788</v>
+        <v>0.410646378993988</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2713567912578583</v>
+        <v>0.404580146074295</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2647058963775635</v>
+        <v>0.4182509481906891</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1003369241952896</v>
+        <v>0.1065522581338882</v>
       </c>
       <c r="K4" t="n">
-        <v>14.1773533821106</v>
+        <v>18.72127771377563</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0497278928756713</v>
+        <v>0.035446982383728</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0476158332824707</v>
+        <v>0.0740448093414306</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0408983612060546</v>
+        <v>0.08027122497558591</v>
       </c>
       <c r="O4" t="n">
-        <v>2.486394643783569</v>
+        <v>1.772349119186401</v>
       </c>
       <c r="P4" t="n">
-        <v>2.380791664123535</v>
+        <v>3.702240467071533</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.044918060302734</v>
+        <v>4.013561248779297</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250702-073907</t>
+          <t>20250627-153058</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -8669,56 +8669,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="C5" t="n">
-        <v>97.41222643852234</v>
+        <v>41.43975615501404</v>
       </c>
       <c r="D5" t="n">
-        <v>5.360000133514404</v>
+        <v>6.480000019073486</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1013361258908759</v>
+        <v>0.1436606773308344</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5714285969734192</v>
+        <v>0.6666666865348816</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3485477268695831</v>
+        <v>0.4308943152427673</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3349282443523407</v>
+        <v>0.3877550959587097</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3188405930995941</v>
+        <v>0.3888888955116272</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0918362513184547</v>
+        <v>0.0933509916067123</v>
       </c>
       <c r="K5" t="n">
-        <v>8.539034366607666</v>
+        <v>13.55183410644531</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0420378112792968</v>
+        <v>0.0399737977981567</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0547505855560302</v>
+        <v>0.07663602828979491</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0404203081130981</v>
+        <v>0.0823387384414672</v>
       </c>
       <c r="O5" t="n">
-        <v>2.101890563964844</v>
+        <v>1.998689889907837</v>
       </c>
       <c r="P5" t="n">
-        <v>2.737529277801514</v>
+        <v>3.831801414489746</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.021015405654907</v>
+        <v>4.116936922073364</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250702-074052</t>
+          <t>20250627-153315</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -8790,56 +8790,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C6" t="n">
-        <v>49.76971101760864</v>
+        <v>38.67496919631958</v>
       </c>
       <c r="D6" t="n">
-        <v>5.349999904632568</v>
+        <v>6.460000038146973</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1000134426867589</v>
+        <v>0.1468710858713496</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.5714285969734192</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2468354403972625</v>
+        <v>0.3523809611797333</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2043010741472244</v>
+        <v>0.3482587039470672</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2054053992033004</v>
+        <v>0.3351351320743561</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08576572686433789</v>
+        <v>0.1106521114706993</v>
       </c>
       <c r="K6" t="n">
-        <v>14.10144972801208</v>
+        <v>13.34319877624512</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0461430883407592</v>
+        <v>0.0389455795288085</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0466438484191894</v>
+        <v>0.0779582786560058</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0408851861953735</v>
+        <v>0.08537075042724609</v>
       </c>
       <c r="O6" t="n">
-        <v>2.307154417037964</v>
+        <v>1.94727897644043</v>
       </c>
       <c r="P6" t="n">
-        <v>2.332192420959473</v>
+        <v>3.897913932800293</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.044259309768677</v>
+        <v>4.268537521362305</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250702-074320</t>
+          <t>20250627-153459</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -9077,56 +9077,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C2" t="n">
-        <v>72.18147540092468</v>
+        <v>47.35507535934448</v>
       </c>
       <c r="D2" t="n">
-        <v>7.449999809265137</v>
+        <v>1.679999947547913</v>
       </c>
       <c r="E2" t="n">
-        <v>0.15813107509166</v>
+        <v>0.1093312573887533</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6666666865348816</v>
+        <v>0.5714285969734192</v>
       </c>
       <c r="G2" t="n">
-        <v>0.30158731341362</v>
+        <v>0.402010053396225</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2588235437870025</v>
+        <v>0.3894736766815185</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2603550255298614</v>
+        <v>0.2569832503795624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.07314231246709819</v>
+        <v>0.09124407917261119</v>
       </c>
       <c r="K2" t="n">
-        <v>30.05579113960266</v>
+        <v>9.597659587860107</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0548881387710571</v>
+        <v>0.0438233089447021</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1230123424530029</v>
+        <v>0.0522859764099121</v>
       </c>
       <c r="N2" t="n">
-        <v>0.092983546257019</v>
+        <v>0.0555906820297241</v>
       </c>
       <c r="O2" t="n">
-        <v>2.744406938552856</v>
+        <v>2.191165447235107</v>
       </c>
       <c r="P2" t="n">
-        <v>6.150617122650146</v>
+        <v>2.614298820495605</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.649177312850952</v>
+        <v>2.779534101486206</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250703-093153</t>
+          <t>20250701-175719</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -9198,56 +9198,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C3" t="n">
-        <v>56.18672132492065</v>
+        <v>58.06486487388611</v>
       </c>
       <c r="D3" t="n">
-        <v>7.46999979019165</v>
+        <v>1.700000047683716</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1580067915575844</v>
+        <v>0.108183067694709</v>
       </c>
       <c r="F3" t="n">
         <v>0.5454545617103577</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2461538463830948</v>
+        <v>0.3636363744735718</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2111111134290695</v>
+        <v>0.2696629166603088</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2134831398725509</v>
+        <v>0.2476190477609634</v>
       </c>
       <c r="J3" t="n">
-        <v>0.09393360465764999</v>
+        <v>0.0845824927091598</v>
       </c>
       <c r="K3" t="n">
-        <v>29.89526319503784</v>
+        <v>15.36320495605469</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0548953914642333</v>
+        <v>0.0424841737747192</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1305882310867309</v>
+        <v>0.0449059391021728</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09062474250793449</v>
+        <v>0.057069764137268</v>
       </c>
       <c r="O3" t="n">
-        <v>2.74476957321167</v>
+        <v>2.124208688735962</v>
       </c>
       <c r="P3" t="n">
-        <v>6.529411554336548</v>
+        <v>2.245296955108643</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.531237125396729</v>
+        <v>2.853488206863404</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250703-093434</t>
+          <t>20250701-175859</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -9319,56 +9319,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="C4" t="n">
-        <v>74.12175035476685</v>
+        <v>69.97928071022034</v>
       </c>
       <c r="D4" t="n">
-        <v>7.449999809265137</v>
+        <v>1.730000019073486</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1584733789381773</v>
+        <v>0.1094247883792673</v>
       </c>
       <c r="F4" t="n">
         <v>0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3361344635486603</v>
+        <v>0.3507462739944458</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2424242496490478</v>
+        <v>0.2119205296039581</v>
       </c>
       <c r="I4" t="n">
-        <v>0.22891566157341</v>
+        <v>0.2564102709293365</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0784569904208183</v>
+        <v>0.07790890336036679</v>
       </c>
       <c r="K4" t="n">
-        <v>29.85474157333374</v>
+        <v>15.18374991416931</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0557406616210937</v>
+        <v>0.0431840229034423</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1237587785720825</v>
+        <v>0.0457931900024414</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0902227306365966</v>
+        <v>0.0575720357894897</v>
       </c>
       <c r="O4" t="n">
-        <v>2.787033081054688</v>
+        <v>2.159201145172119</v>
       </c>
       <c r="P4" t="n">
-        <v>6.187938928604126</v>
+        <v>2.28965950012207</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.511136531829834</v>
+        <v>2.878601789474488</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250703-093658</t>
+          <t>20250701-180056</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -9440,56 +9440,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="C5" t="n">
-        <v>111.5439441204071</v>
+        <v>43.8674783706665</v>
       </c>
       <c r="D5" t="n">
-        <v>7.46999979019165</v>
+        <v>1.679999947547913</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1592088520813446</v>
+        <v>0.1095885615105981</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5714285969734192</v>
+        <v>0.6153846383094788</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4623115658760071</v>
+        <v>0.409090906381607</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2857142984867096</v>
+        <v>0.3655914068222046</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3253012001514435</v>
+        <v>0.3617021143436432</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08432570099830621</v>
+        <v>0.0862606987357139</v>
       </c>
       <c r="K5" t="n">
-        <v>29.52331614494324</v>
+        <v>9.615137100219728</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0543894910812377</v>
+        <v>0.0498618030548095</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1230439281463623</v>
+        <v>0.0448733615875244</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09098366737365721</v>
+        <v>0.0631472969055175</v>
       </c>
       <c r="O5" t="n">
-        <v>2.71947455406189</v>
+        <v>2.493090152740479</v>
       </c>
       <c r="P5" t="n">
-        <v>6.152196407318115</v>
+        <v>2.243668079376221</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.549183368682861</v>
+        <v>3.157364845275879</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250703-093940</t>
+          <t>20250701-180304</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -9561,56 +9561,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n">
-        <v>65.65304136276245</v>
+        <v>31.81498122215271</v>
       </c>
       <c r="D6" t="n">
-        <v>7.46999979019165</v>
+        <v>1.679999947547913</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1581651467387958</v>
+        <v>0.1065796220149749</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5714285969734192</v>
+        <v>0.3636363744735718</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2083333283662796</v>
+        <v>0.2842105329036712</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2245989292860031</v>
+        <v>0.2622950673103332</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2352941185235977</v>
+        <v>0.2555555701255798</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0753104016184806</v>
+        <v>0.1333552151918411</v>
       </c>
       <c r="K6" t="n">
-        <v>29.57910537719727</v>
+        <v>9.734108448028564</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0534311628341674</v>
+        <v>0.0471098804473876</v>
       </c>
       <c r="M6" t="n">
-        <v>0.122987003326416</v>
+        <v>0.0447437477111816</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0903075885772705</v>
+        <v>0.06300902366638179</v>
       </c>
       <c r="O6" t="n">
-        <v>2.671558141708374</v>
+        <v>2.355494022369385</v>
       </c>
       <c r="P6" t="n">
-        <v>6.149350166320801</v>
+        <v>2.237187385559082</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.515379428863525</v>
+        <v>3.150451183319092</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250703-094258</t>
+          <t>20250701-180446</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
